--- a/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 14,28</t>
+          <t>0,39; 14,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 5,69</t>
+          <t>-8,34; 5,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 17,39</t>
+          <t>-0,28; 16,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 606,93</t>
+          <t>-10,42; 591,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 99,39</t>
+          <t>-64,69; 93,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 206,73</t>
+          <t>-3,55; 175,74</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,13</t>
+          <t>-5,5; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 2,74</t>
+          <t>-8,05; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,25</t>
+          <t>-7,45; 5,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-89,83; 250,58</t>
+          <t>-88,29; 285,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,95; 69,54</t>
+          <t>-77,95; 62,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,02; 131,02</t>
+          <t>-67,47; 107,74</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,38</t>
+          <t>-3,04; 3,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 10,66</t>
+          <t>0,29; 10,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 4,1</t>
+          <t>-11,59; 5,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 148,5</t>
+          <t>-83,95; 142,71</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,39</t>
+          <t>-4,42; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,61</t>
+          <t>-0,94; 3,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,15</t>
+          <t>-4,51; 3,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,62; 42,07</t>
+          <t>-87,48; 38,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 793,81</t>
+          <t>-52,68; 574,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 94,95</t>
+          <t>-53,67; 92,57</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,31</t>
+          <t>0,01; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,52</t>
+          <t>-2,59; 1,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,08</t>
+          <t>-2,15; 4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-55,39; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,19; 429,3</t>
+          <t>-67,38; 410,23</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,1</t>
+          <t>-7,83; 2,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,25</t>
+          <t>-3,15; 5,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,34</t>
+          <t>-6,03; 6,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 339,83</t>
+          <t>-78,67; 449,45</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,06</t>
+          <t>-0,93; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,75</t>
+          <t>-1,44; 1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,94</t>
+          <t>-1,08; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 89,45</t>
+          <t>-28,47; 98,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 66,55</t>
+          <t>-34,31; 64,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 69,03</t>
+          <t>-14,38; 66,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 14,08</t>
+          <t>-0,15; 13,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 5,35</t>
+          <t>-7,93; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 16,36</t>
+          <t>0,74; 16,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 591,6</t>
+          <t>-13,57; 588,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 93,88</t>
+          <t>-61,6; 114,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 175,74</t>
+          <t>2,84; 180,41</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 3,02</t>
+          <t>-5,47; 3,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 2,36</t>
+          <t>-7,43; 2,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,31</t>
+          <t>-7,45; 4,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 285,55</t>
+          <t>-86,24; 277,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 62,6</t>
+          <t>-79,47; 68,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 107,74</t>
+          <t>-67,89; 113,43</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,46</t>
+          <t>-3,17; 3,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,68</t>
+          <t>0,25; 10,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 5,26</t>
+          <t>-11,52; 5,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 142,71</t>
+          <t>-83,43; 169,25</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,54</t>
+          <t>-4,19; 0,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,51</t>
+          <t>-0,85; 3,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,86</t>
+          <t>-4,24; 4,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 38,64</t>
+          <t>-86,79; 38,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 574,23</t>
+          <t>-45,39; 851,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 92,57</t>
+          <t>-51,24; 93,91</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,82</t>
+          <t>0,19; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,93</t>
+          <t>-2,72; 1,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,37</t>
+          <t>-1,92; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-55,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 410,23</t>
+          <t>-61,15; 554,06</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 2,06</t>
+          <t>-8,01; 2,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,48</t>
+          <t>-3,22; 6,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,67</t>
+          <t>-5,25; 7,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,67; 449,45</t>
+          <t>-73,42; 458,17</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,03</t>
+          <t>-1,02; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,64</t>
+          <t>-1,53; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,66</t>
+          <t>-1,15; 3,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 98,3</t>
+          <t>-28,34; 94,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 64,43</t>
+          <t>-35,26; 68,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 66,05</t>
+          <t>-14,54; 63,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Clase-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 13,51</t>
+          <t>0,28; 14,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 6,2</t>
+          <t>-8,82; 5,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 16,88</t>
+          <t>1,21; 17,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 588,25</t>
+          <t>-7,58; 606,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,6; 114,77</t>
+          <t>-63,27; 99,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 180,41</t>
+          <t>3,78; 203,58</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-11,18%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,01</t>
+          <t>-5,92; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 2,64</t>
+          <t>-7,58; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 4,93</t>
+          <t>-7,79; 5,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 277,03</t>
+          <t>-89,83; 250,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,47; 68,65</t>
+          <t>-75,95; 69,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 113,43</t>
+          <t>-68,42; 149,62</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-34,23%</t>
+          <t>-36,5%</t>
         </is>
       </c>
     </row>
@@ -792,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,28</t>
+          <t>-3,08; 3,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 10,82</t>
+          <t>-0,32; 10,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 5,99</t>
+          <t>-11,37; 4,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,43; 169,25</t>
+          <t>-85,15; 147,58</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,4</t>
+          <t>-4,42; 0,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,87</t>
+          <t>-0,84; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,12</t>
+          <t>-2,7; 6,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 38,32</t>
+          <t>-87,62; 42,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 851,7</t>
+          <t>-45,59; 793,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 93,91</t>
+          <t>-35,92; 137,94</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,87</t>
+          <t>-0,33; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,62</t>
+          <t>-3,01; 1,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,2</t>
+          <t>-2,14; 4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 554,06</t>
+          <t>-66,47; 432,21</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 2,06</t>
+          <t>-8,34; 2,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,33</t>
+          <t>-3,13; 6,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 7,04</t>
+          <t>-3,13; 8,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1057,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 458,17</t>
+          <t>-63,65; 711,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,05</t>
+          <t>-1,09; 2,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,87</t>
+          <t>-1,5; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,68</t>
+          <t>-0,42; 4,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 94,69</t>
+          <t>-31,7; 89,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 68,95</t>
+          <t>-35,23; 66,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 63,05</t>
+          <t>-6,22; 80,36</t>
         </is>
       </c>
     </row>
